--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117884599</v>
       </c>
       <c r="B2" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,116 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128990099</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>489372</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6945685</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128990099</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,226 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129744402</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489337</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6945936</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129744454</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489338</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6945928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129744402</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129744454</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117884599</v>
       </c>
       <c r="B2" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128990099</v>
+        <v>117884619</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,46 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högtjärn, Jmt</t>
+          <t>långberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489372</v>
+        <v>489356</v>
       </c>
       <c r="R3" t="n">
-        <v>6945685</v>
+        <v>6945937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,69 +885,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129744402</v>
+        <v>128485680</v>
       </c>
       <c r="B4" t="n">
-        <v>98830</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högtjärn, Jmt</t>
+          <t>Högtjärn , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489337</v>
+        <v>489366</v>
       </c>
       <c r="R4" t="n">
-        <v>6945936</v>
+        <v>6945991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,46 +998,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129744454</v>
+        <v>128485716</v>
       </c>
       <c r="B5" t="n">
-        <v>98830</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489338</v>
+        <v>489325</v>
       </c>
       <c r="R5" t="n">
-        <v>6945928</v>
+        <v>6945995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,6 +1096,882 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128677495</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489325</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6945995</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128990099</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489372</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6945685</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128990127</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489351</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6945685</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129546230</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högtjärn, Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489327</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6945906</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129744365</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489363</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6945911</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129744383</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489367</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6945927</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129744402</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489337</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6945936</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129744454</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489338</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6945928</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47-2023 artfynd.xlsx
+++ b/artfynd/A 47-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117884619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128990127</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129546230</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744365</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744383</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744402</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1972,8 +2032,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>